--- a/artfynd/A 32232-2026 artfynd.xlsx
+++ b/artfynd/A 32232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825519</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825559</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825253</v>
       </c>
       <c r="B4" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135825511</v>
       </c>
       <c r="B5" t="n">
-        <v>92032</v>
+        <v>92034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>135810576</v>
       </c>
       <c r="B79" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>135825534</v>
       </c>
       <c r="B80" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>135825749</v>
       </c>
       <c r="B81" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>135825755</v>
       </c>
       <c r="B82" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 32232-2026 artfynd.xlsx
+++ b/artfynd/A 32232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825519</v>
       </c>
       <c r="B2" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825559</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825253</v>
       </c>
       <c r="B4" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135825511</v>
       </c>
       <c r="B5" t="n">
-        <v>92034</v>
+        <v>92048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135824116</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>135824129</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>135824190</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135824233</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135824366</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>135824376</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>135824407</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>135824423</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>135824441</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135824529</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>135824763</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135824777</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135825233</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>135825278</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>135825365</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>135825387</v>
       </c>
       <c r="B21" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>135825403</v>
       </c>
       <c r="B22" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>135825422</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>135825434</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>135825440</v>
       </c>
       <c r="B25" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>135825478</v>
       </c>
       <c r="B26" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>135825486</v>
       </c>
       <c r="B27" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135825568</v>
       </c>
       <c r="B28" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>135825576</v>
       </c>
       <c r="B29" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>135825599</v>
       </c>
       <c r="B30" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>135825613</v>
       </c>
       <c r="B31" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>135825639</v>
       </c>
       <c r="B32" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>135825791</v>
       </c>
       <c r="B33" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>135825887</v>
       </c>
       <c r="B34" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>135825897</v>
       </c>
       <c r="B35" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135824144</v>
       </c>
       <c r="B36" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>135825877</v>
       </c>
       <c r="B37" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>135814188</v>
       </c>
       <c r="B38" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>135817143</v>
       </c>
       <c r="B39" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135810534</v>
       </c>
       <c r="B40" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>135812552</v>
       </c>
       <c r="B41" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>135812794</v>
       </c>
       <c r="B42" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>135817457</v>
       </c>
       <c r="B43" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135825727</v>
       </c>
       <c r="B44" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>135825937</v>
       </c>
       <c r="B45" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>135825994</v>
       </c>
       <c r="B46" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>135810638</v>
       </c>
       <c r="B47" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>135810678</v>
       </c>
       <c r="B48" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>135810752</v>
       </c>
       <c r="B49" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>135811260</v>
       </c>
       <c r="B50" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>135811380</v>
       </c>
       <c r="B51" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>135811775</v>
       </c>
       <c r="B52" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>135811889</v>
       </c>
       <c r="B53" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>135812149</v>
       </c>
       <c r="B54" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>135812282</v>
       </c>
       <c r="B55" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>135812304</v>
       </c>
       <c r="B56" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>135812678</v>
       </c>
       <c r="B57" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>135813207</v>
       </c>
       <c r="B58" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>135813220</v>
       </c>
       <c r="B59" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>135813260</v>
       </c>
       <c r="B60" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>135813643</v>
       </c>
       <c r="B61" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>135813806</v>
       </c>
       <c r="B62" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>135815937</v>
       </c>
       <c r="B63" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>135816847</v>
       </c>
       <c r="B64" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>135817411</v>
       </c>
       <c r="B65" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>135817908</v>
       </c>
       <c r="B66" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>135818950</v>
       </c>
       <c r="B67" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>135820000</v>
       </c>
       <c r="B68" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>135820108</v>
       </c>
       <c r="B69" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135820167</v>
       </c>
       <c r="B70" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>135820223</v>
       </c>
       <c r="B71" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>135824350</v>
       </c>
       <c r="B72" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>135824747</v>
       </c>
       <c r="B73" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>135824805</v>
       </c>
       <c r="B74" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>135825271</v>
       </c>
       <c r="B75" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>135825839</v>
       </c>
       <c r="B76" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>135826009</v>
       </c>
       <c r="B77" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>135817961</v>
       </c>
       <c r="B78" t="n">
-        <v>57158</v>
+        <v>57160</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>135810576</v>
       </c>
       <c r="B79" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>135825534</v>
       </c>
       <c r="B80" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>135825749</v>
       </c>
       <c r="B81" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>135825755</v>
       </c>
       <c r="B82" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>135824162</v>
       </c>
       <c r="B83" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>135824255</v>
       </c>
       <c r="B84" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>135825266</v>
       </c>
       <c r="B85" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 32232-2026 artfynd.xlsx
+++ b/artfynd/A 32232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825519</v>
       </c>
       <c r="B2" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825559</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825253</v>
       </c>
       <c r="B4" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135825511</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135824116</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>135824129</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>135824190</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135824233</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135824366</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>135824376</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>135824407</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>135824423</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>135824441</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135824529</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>135824763</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135824777</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135825233</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>135825278</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>135825365</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>135825387</v>
       </c>
       <c r="B21" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>135825403</v>
       </c>
       <c r="B22" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>135825422</v>
       </c>
       <c r="B23" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>135825434</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>135825440</v>
       </c>
       <c r="B25" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>135825478</v>
       </c>
       <c r="B26" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>135825486</v>
       </c>
       <c r="B27" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135825568</v>
       </c>
       <c r="B28" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>135825576</v>
       </c>
       <c r="B29" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>135825599</v>
       </c>
       <c r="B30" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>135825613</v>
       </c>
       <c r="B31" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>135825639</v>
       </c>
       <c r="B32" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>135825791</v>
       </c>
       <c r="B33" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>135825887</v>
       </c>
       <c r="B34" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>135825897</v>
       </c>
       <c r="B35" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135824144</v>
       </c>
       <c r="B36" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>135825877</v>
       </c>
       <c r="B37" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>135810576</v>
       </c>
       <c r="B79" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>135825534</v>
       </c>
       <c r="B80" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>135825749</v>
       </c>
       <c r="B81" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>135825755</v>
       </c>
       <c r="B82" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>135824162</v>
       </c>
       <c r="B83" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>135824255</v>
       </c>
       <c r="B84" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>135825266</v>
       </c>
       <c r="B85" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 32232-2026 artfynd.xlsx
+++ b/artfynd/A 32232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825519</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825559</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825253</v>
       </c>
       <c r="B4" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135825511</v>
       </c>
       <c r="B5" t="n">
-        <v>92049</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>135810576</v>
       </c>
       <c r="B79" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>135825534</v>
       </c>
       <c r="B80" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>135825749</v>
       </c>
       <c r="B81" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>135825755</v>
       </c>
       <c r="B82" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 32232-2026 artfynd.xlsx
+++ b/artfynd/A 32232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825519</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825559</v>
       </c>
       <c r="B3" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825253</v>
       </c>
       <c r="B4" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135825511</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135824116</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>135824129</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>135824190</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135824233</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135824366</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>135824376</v>
       </c>
       <c r="B11" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>135824407</v>
       </c>
       <c r="B12" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>135824423</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>135824441</v>
       </c>
       <c r="B14" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135824529</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>135824763</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135824777</v>
       </c>
       <c r="B17" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135825233</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>135825278</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>135825365</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>135825387</v>
       </c>
       <c r="B21" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>135825403</v>
       </c>
       <c r="B22" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>135825422</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>135825434</v>
       </c>
       <c r="B24" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>135825440</v>
       </c>
       <c r="B25" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>135825478</v>
       </c>
       <c r="B26" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>135825486</v>
       </c>
       <c r="B27" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135825568</v>
       </c>
       <c r="B28" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>135825576</v>
       </c>
       <c r="B29" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>135825599</v>
       </c>
       <c r="B30" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>135825613</v>
       </c>
       <c r="B31" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>135825639</v>
       </c>
       <c r="B32" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>135825791</v>
       </c>
       <c r="B33" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>135825887</v>
       </c>
       <c r="B34" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>135825897</v>
       </c>
       <c r="B35" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135824144</v>
       </c>
       <c r="B36" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>135825877</v>
       </c>
       <c r="B37" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>135814188</v>
       </c>
       <c r="B38" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>135817143</v>
       </c>
       <c r="B39" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135810534</v>
       </c>
       <c r="B40" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>135812552</v>
       </c>
       <c r="B41" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>135812794</v>
       </c>
       <c r="B42" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>135817457</v>
       </c>
       <c r="B43" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135825727</v>
       </c>
       <c r="B44" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>135825937</v>
       </c>
       <c r="B45" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>135825994</v>
       </c>
       <c r="B46" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>135810638</v>
       </c>
       <c r="B47" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>135810678</v>
       </c>
       <c r="B48" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>135810752</v>
       </c>
       <c r="B49" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>135811260</v>
       </c>
       <c r="B50" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>135811380</v>
       </c>
       <c r="B51" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>135811775</v>
       </c>
       <c r="B52" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>135811889</v>
       </c>
       <c r="B53" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>135812149</v>
       </c>
       <c r="B54" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>135812282</v>
       </c>
       <c r="B55" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>135812304</v>
       </c>
       <c r="B56" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>135812678</v>
       </c>
       <c r="B57" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>135813207</v>
       </c>
       <c r="B58" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>135813220</v>
       </c>
       <c r="B59" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>135813260</v>
       </c>
       <c r="B60" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>135813643</v>
       </c>
       <c r="B61" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>135813806</v>
       </c>
       <c r="B62" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>135815937</v>
       </c>
       <c r="B63" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>135816847</v>
       </c>
       <c r="B64" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>135817411</v>
       </c>
       <c r="B65" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>135817908</v>
       </c>
       <c r="B66" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>135818950</v>
       </c>
       <c r="B67" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>135820000</v>
       </c>
       <c r="B68" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>135820108</v>
       </c>
       <c r="B69" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135820167</v>
       </c>
       <c r="B70" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>135820223</v>
       </c>
       <c r="B71" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>135824350</v>
       </c>
       <c r="B72" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>135824747</v>
       </c>
       <c r="B73" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>135824805</v>
       </c>
       <c r="B74" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>135825271</v>
       </c>
       <c r="B75" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>135825839</v>
       </c>
       <c r="B76" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>135826009</v>
       </c>
       <c r="B77" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>135817961</v>
       </c>
       <c r="B78" t="n">
-        <v>57160</v>
+        <v>57161</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>135810576</v>
       </c>
       <c r="B79" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>135825534</v>
       </c>
       <c r="B80" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>135825749</v>
       </c>
       <c r="B81" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>135825755</v>
       </c>
       <c r="B82" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>135824162</v>
       </c>
       <c r="B83" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>135824255</v>
       </c>
       <c r="B84" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>135825266</v>
       </c>
       <c r="B85" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 32232-2026 artfynd.xlsx
+++ b/artfynd/A 32232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825519</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825559</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825253</v>
       </c>
       <c r="B4" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135825511</v>
       </c>
       <c r="B5" t="n">
-        <v>92051</v>
+        <v>92057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135824116</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>135824129</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>135824190</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135824233</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135824366</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>135824376</v>
       </c>
       <c r="B11" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>135824407</v>
       </c>
       <c r="B12" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>135824423</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>135824441</v>
       </c>
       <c r="B14" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135824529</v>
       </c>
       <c r="B15" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>135824763</v>
       </c>
       <c r="B16" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135824777</v>
       </c>
       <c r="B17" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135825233</v>
       </c>
       <c r="B18" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>135825278</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>135825365</v>
       </c>
       <c r="B20" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>135825387</v>
       </c>
       <c r="B21" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>135825403</v>
       </c>
       <c r="B22" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>135825422</v>
       </c>
       <c r="B23" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>135825434</v>
       </c>
       <c r="B24" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>135825440</v>
       </c>
       <c r="B25" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>135825478</v>
       </c>
       <c r="B26" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>135825486</v>
       </c>
       <c r="B27" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135825568</v>
       </c>
       <c r="B28" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>135825576</v>
       </c>
       <c r="B29" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>135825599</v>
       </c>
       <c r="B30" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>135825613</v>
       </c>
       <c r="B31" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>135825639</v>
       </c>
       <c r="B32" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>135825791</v>
       </c>
       <c r="B33" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>135825887</v>
       </c>
       <c r="B34" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>135825897</v>
       </c>
       <c r="B35" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135824144</v>
       </c>
       <c r="B36" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>135825877</v>
       </c>
       <c r="B37" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>135814188</v>
       </c>
       <c r="B38" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>135817143</v>
       </c>
       <c r="B39" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135810534</v>
       </c>
       <c r="B40" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>135812552</v>
       </c>
       <c r="B41" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>135812794</v>
       </c>
       <c r="B42" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>135817457</v>
       </c>
       <c r="B43" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135825727</v>
       </c>
       <c r="B44" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>135825937</v>
       </c>
       <c r="B45" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>135825994</v>
       </c>
       <c r="B46" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>135810638</v>
       </c>
       <c r="B47" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>135810678</v>
       </c>
       <c r="B48" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>135810752</v>
       </c>
       <c r="B49" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>135811260</v>
       </c>
       <c r="B50" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>135811380</v>
       </c>
       <c r="B51" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>135811775</v>
       </c>
       <c r="B52" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>135811889</v>
       </c>
       <c r="B53" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>135812149</v>
       </c>
       <c r="B54" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>135812282</v>
       </c>
       <c r="B55" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>135812304</v>
       </c>
       <c r="B56" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>135812678</v>
       </c>
       <c r="B57" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>135813207</v>
       </c>
       <c r="B58" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>135813220</v>
       </c>
       <c r="B59" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>135813260</v>
       </c>
       <c r="B60" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>135813643</v>
       </c>
       <c r="B61" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>135813806</v>
       </c>
       <c r="B62" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>135815937</v>
       </c>
       <c r="B63" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>135816847</v>
       </c>
       <c r="B64" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>135817411</v>
       </c>
       <c r="B65" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>135817908</v>
       </c>
       <c r="B66" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>135818950</v>
       </c>
       <c r="B67" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>135820000</v>
       </c>
       <c r="B68" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>135820108</v>
       </c>
       <c r="B69" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135820167</v>
       </c>
       <c r="B70" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>135820223</v>
       </c>
       <c r="B71" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>135824350</v>
       </c>
       <c r="B72" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>135824747</v>
       </c>
       <c r="B73" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>135824805</v>
       </c>
       <c r="B74" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>135825271</v>
       </c>
       <c r="B75" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>135825839</v>
       </c>
       <c r="B76" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>135826009</v>
       </c>
       <c r="B77" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>135817961</v>
       </c>
       <c r="B78" t="n">
-        <v>57161</v>
+        <v>57165</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>135810576</v>
       </c>
       <c r="B79" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>135825534</v>
       </c>
       <c r="B80" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>135825749</v>
       </c>
       <c r="B81" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>135825755</v>
       </c>
       <c r="B82" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>135824162</v>
       </c>
       <c r="B83" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>135824255</v>
       </c>
       <c r="B84" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>135825266</v>
       </c>
       <c r="B85" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 32232-2026 artfynd.xlsx
+++ b/artfynd/A 32232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825519</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825559</v>
       </c>
       <c r="B3" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825253</v>
       </c>
       <c r="B4" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135825511</v>
       </c>
       <c r="B5" t="n">
-        <v>92057</v>
+        <v>92058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135824116</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>135824129</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>135824190</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135824233</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135824366</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>135824376</v>
       </c>
       <c r="B11" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>135824407</v>
       </c>
       <c r="B12" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>135824423</v>
       </c>
       <c r="B13" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>135824441</v>
       </c>
       <c r="B14" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135824529</v>
       </c>
       <c r="B15" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>135824763</v>
       </c>
       <c r="B16" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135824777</v>
       </c>
       <c r="B17" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135825233</v>
       </c>
       <c r="B18" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>135825278</v>
       </c>
       <c r="B19" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>135825365</v>
       </c>
       <c r="B20" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>135825387</v>
       </c>
       <c r="B21" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>135825403</v>
       </c>
       <c r="B22" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>135825422</v>
       </c>
       <c r="B23" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>135825434</v>
       </c>
       <c r="B24" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>135825440</v>
       </c>
       <c r="B25" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>135825478</v>
       </c>
       <c r="B26" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>135825486</v>
       </c>
       <c r="B27" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135825568</v>
       </c>
       <c r="B28" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>135825576</v>
       </c>
       <c r="B29" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>135825599</v>
       </c>
       <c r="B30" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>135825613</v>
       </c>
       <c r="B31" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>135825639</v>
       </c>
       <c r="B32" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>135825791</v>
       </c>
       <c r="B33" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>135825887</v>
       </c>
       <c r="B34" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>135825897</v>
       </c>
       <c r="B35" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135824144</v>
       </c>
       <c r="B36" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>135825877</v>
       </c>
       <c r="B37" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>135814188</v>
       </c>
       <c r="B38" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>135817143</v>
       </c>
       <c r="B39" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135810534</v>
       </c>
       <c r="B40" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>135812552</v>
       </c>
       <c r="B41" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>135812794</v>
       </c>
       <c r="B42" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>135817457</v>
       </c>
       <c r="B43" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135825727</v>
       </c>
       <c r="B44" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>135825937</v>
       </c>
       <c r="B45" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>135825994</v>
       </c>
       <c r="B46" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>135810638</v>
       </c>
       <c r="B47" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>135810678</v>
       </c>
       <c r="B48" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>135810752</v>
       </c>
       <c r="B49" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>135811260</v>
       </c>
       <c r="B50" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>135811380</v>
       </c>
       <c r="B51" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>135811775</v>
       </c>
       <c r="B52" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>135811889</v>
       </c>
       <c r="B53" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>135812149</v>
       </c>
       <c r="B54" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>135812282</v>
       </c>
       <c r="B55" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>135812304</v>
       </c>
       <c r="B56" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>135812678</v>
       </c>
       <c r="B57" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>135813207</v>
       </c>
       <c r="B58" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>135813220</v>
       </c>
       <c r="B59" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>135813260</v>
       </c>
       <c r="B60" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>135813643</v>
       </c>
       <c r="B61" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>135813806</v>
       </c>
       <c r="B62" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>135815937</v>
       </c>
       <c r="B63" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>135816847</v>
       </c>
       <c r="B64" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>135817411</v>
       </c>
       <c r="B65" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>135817908</v>
       </c>
       <c r="B66" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>135818950</v>
       </c>
       <c r="B67" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>135820000</v>
       </c>
       <c r="B68" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>135820108</v>
       </c>
       <c r="B69" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135820167</v>
       </c>
       <c r="B70" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>135820223</v>
       </c>
       <c r="B71" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>135824350</v>
       </c>
       <c r="B72" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>135824747</v>
       </c>
       <c r="B73" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>135824805</v>
       </c>
       <c r="B74" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>135825271</v>
       </c>
       <c r="B75" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>135825839</v>
       </c>
       <c r="B76" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>135826009</v>
       </c>
       <c r="B77" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>135817961</v>
       </c>
       <c r="B78" t="n">
-        <v>57165</v>
+        <v>57166</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>135810576</v>
       </c>
       <c r="B79" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>135825534</v>
       </c>
       <c r="B80" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>135825749</v>
       </c>
       <c r="B81" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>135825755</v>
       </c>
       <c r="B82" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>135824162</v>
       </c>
       <c r="B83" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>135824255</v>
       </c>
       <c r="B84" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>135825266</v>
       </c>
       <c r="B85" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 32232-2026 artfynd.xlsx
+++ b/artfynd/A 32232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825519</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825559</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825253</v>
       </c>
       <c r="B4" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135825511</v>
       </c>
       <c r="B5" t="n">
-        <v>92058</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135824116</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>135824129</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>135824190</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135824233</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135824366</v>
       </c>
       <c r="B10" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>135824376</v>
       </c>
       <c r="B11" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>135824407</v>
       </c>
       <c r="B12" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>135824423</v>
       </c>
       <c r="B13" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>135824441</v>
       </c>
       <c r="B14" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135824529</v>
       </c>
       <c r="B15" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>135824763</v>
       </c>
       <c r="B16" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135824777</v>
       </c>
       <c r="B17" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135825233</v>
       </c>
       <c r="B18" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>135825278</v>
       </c>
       <c r="B19" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>135825365</v>
       </c>
       <c r="B20" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>135825387</v>
       </c>
       <c r="B21" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>135825403</v>
       </c>
       <c r="B22" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>135825422</v>
       </c>
       <c r="B23" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>135825434</v>
       </c>
       <c r="B24" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>135825440</v>
       </c>
       <c r="B25" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>135825478</v>
       </c>
       <c r="B26" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>135825486</v>
       </c>
       <c r="B27" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135825568</v>
       </c>
       <c r="B28" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>135825576</v>
       </c>
       <c r="B29" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>135825599</v>
       </c>
       <c r="B30" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>135825613</v>
       </c>
       <c r="B31" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>135825639</v>
       </c>
       <c r="B32" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>135825791</v>
       </c>
       <c r="B33" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>135825887</v>
       </c>
       <c r="B34" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>135825897</v>
       </c>
       <c r="B35" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135824144</v>
       </c>
       <c r="B36" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>135825877</v>
       </c>
       <c r="B37" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>135810576</v>
       </c>
       <c r="B79" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>135825534</v>
       </c>
       <c r="B80" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>135825749</v>
       </c>
       <c r="B81" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>135825755</v>
       </c>
       <c r="B82" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>135824162</v>
       </c>
       <c r="B83" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>135824255</v>
       </c>
       <c r="B84" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>135825266</v>
       </c>
       <c r="B85" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 32232-2026 artfynd.xlsx
+++ b/artfynd/A 32232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825519</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825559</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825253</v>
       </c>
       <c r="B4" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135825511</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>92071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135824116</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>135824129</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>135824190</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135824233</v>
       </c>
       <c r="B9" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135824366</v>
       </c>
       <c r="B10" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>135824376</v>
       </c>
       <c r="B11" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>135824407</v>
       </c>
       <c r="B12" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>135824423</v>
       </c>
       <c r="B13" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>135824441</v>
       </c>
       <c r="B14" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135824529</v>
       </c>
       <c r="B15" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>135824763</v>
       </c>
       <c r="B16" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135824777</v>
       </c>
       <c r="B17" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135825233</v>
       </c>
       <c r="B18" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>135825278</v>
       </c>
       <c r="B19" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>135825365</v>
       </c>
       <c r="B20" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>135825387</v>
       </c>
       <c r="B21" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>135825403</v>
       </c>
       <c r="B22" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>135825422</v>
       </c>
       <c r="B23" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>135825434</v>
       </c>
       <c r="B24" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>135825440</v>
       </c>
       <c r="B25" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>135825478</v>
       </c>
       <c r="B26" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>135825486</v>
       </c>
       <c r="B27" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135825568</v>
       </c>
       <c r="B28" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>135825576</v>
       </c>
       <c r="B29" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>135825599</v>
       </c>
       <c r="B30" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>135825613</v>
       </c>
       <c r="B31" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>135825639</v>
       </c>
       <c r="B32" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>135825791</v>
       </c>
       <c r="B33" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>135825887</v>
       </c>
       <c r="B34" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>135825897</v>
       </c>
       <c r="B35" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135824144</v>
       </c>
       <c r="B36" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>135825877</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>135814188</v>
       </c>
       <c r="B38" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>135817143</v>
       </c>
       <c r="B39" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135810534</v>
       </c>
       <c r="B40" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>135812552</v>
       </c>
       <c r="B41" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>135812794</v>
       </c>
       <c r="B42" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>135817457</v>
       </c>
       <c r="B43" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135825727</v>
       </c>
       <c r="B44" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>135825937</v>
       </c>
       <c r="B45" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>135825994</v>
       </c>
       <c r="B46" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>135810638</v>
       </c>
       <c r="B47" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>135810678</v>
       </c>
       <c r="B48" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>135810752</v>
       </c>
       <c r="B49" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>135811260</v>
       </c>
       <c r="B50" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>135811380</v>
       </c>
       <c r="B51" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>135811775</v>
       </c>
       <c r="B52" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>135811889</v>
       </c>
       <c r="B53" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>135812149</v>
       </c>
       <c r="B54" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>135812282</v>
       </c>
       <c r="B55" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>135812304</v>
       </c>
       <c r="B56" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>135812678</v>
       </c>
       <c r="B57" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>135813207</v>
       </c>
       <c r="B58" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>135813220</v>
       </c>
       <c r="B59" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>135813260</v>
       </c>
       <c r="B60" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>135813643</v>
       </c>
       <c r="B61" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>135813806</v>
       </c>
       <c r="B62" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>135815937</v>
       </c>
       <c r="B63" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>135816847</v>
       </c>
       <c r="B64" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>135817411</v>
       </c>
       <c r="B65" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>135817908</v>
       </c>
       <c r="B66" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>135818950</v>
       </c>
       <c r="B67" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>135820000</v>
       </c>
       <c r="B68" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>135820108</v>
       </c>
       <c r="B69" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135820167</v>
       </c>
       <c r="B70" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>135820223</v>
       </c>
       <c r="B71" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>135824350</v>
       </c>
       <c r="B72" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>135824747</v>
       </c>
       <c r="B73" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>135824805</v>
       </c>
       <c r="B74" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>135825271</v>
       </c>
       <c r="B75" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>135825839</v>
       </c>
       <c r="B76" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>135826009</v>
       </c>
       <c r="B77" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>135817961</v>
       </c>
       <c r="B78" t="n">
-        <v>57166</v>
+        <v>57171</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>135810576</v>
       </c>
       <c r="B79" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>135825534</v>
       </c>
       <c r="B80" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>135825749</v>
       </c>
       <c r="B81" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>135825755</v>
       </c>
       <c r="B82" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>135824162</v>
       </c>
       <c r="B83" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>135824255</v>
       </c>
       <c r="B84" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>135825266</v>
       </c>
       <c r="B85" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 32232-2026 artfynd.xlsx
+++ b/artfynd/A 32232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825519</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825559</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825253</v>
       </c>
       <c r="B4" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135825511</v>
       </c>
       <c r="B5" t="n">
-        <v>92071</v>
+        <v>92072</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>135810576</v>
       </c>
       <c r="B79" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>135825534</v>
       </c>
       <c r="B80" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>135825749</v>
       </c>
       <c r="B81" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>135825755</v>
       </c>
       <c r="B82" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 32232-2026 artfynd.xlsx
+++ b/artfynd/A 32232-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135825519</v>
       </c>
       <c r="B2" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135825559</v>
       </c>
       <c r="B3" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135825253</v>
       </c>
       <c r="B4" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135825511</v>
       </c>
       <c r="B5" t="n">
-        <v>92072</v>
+        <v>92085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135824116</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>135824129</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>135824190</v>
       </c>
       <c r="B8" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135824233</v>
       </c>
       <c r="B9" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135824366</v>
       </c>
       <c r="B10" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>135824376</v>
       </c>
       <c r="B11" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>135824407</v>
       </c>
       <c r="B12" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>135824423</v>
       </c>
       <c r="B13" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>135824441</v>
       </c>
       <c r="B14" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>135824529</v>
       </c>
       <c r="B15" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>135824763</v>
       </c>
       <c r="B16" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135824777</v>
       </c>
       <c r="B17" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135825233</v>
       </c>
       <c r="B18" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>135825278</v>
       </c>
       <c r="B19" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>135825365</v>
       </c>
       <c r="B20" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>135825387</v>
       </c>
       <c r="B21" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>135825403</v>
       </c>
       <c r="B22" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>135825422</v>
       </c>
       <c r="B23" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>135825434</v>
       </c>
       <c r="B24" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>135825440</v>
       </c>
       <c r="B25" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>135825478</v>
       </c>
       <c r="B26" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>135825486</v>
       </c>
       <c r="B27" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135825568</v>
       </c>
       <c r="B28" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>135825576</v>
       </c>
       <c r="B29" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>135825599</v>
       </c>
       <c r="B30" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>135825613</v>
       </c>
       <c r="B31" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>135825639</v>
       </c>
       <c r="B32" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>135825791</v>
       </c>
       <c r="B33" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>135825887</v>
       </c>
       <c r="B34" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>135825897</v>
       </c>
       <c r="B35" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135824144</v>
       </c>
       <c r="B36" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>135825877</v>
       </c>
       <c r="B37" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>135814188</v>
       </c>
       <c r="B38" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>135817143</v>
       </c>
       <c r="B39" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135810534</v>
       </c>
       <c r="B40" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>135812552</v>
       </c>
       <c r="B41" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>135812794</v>
       </c>
       <c r="B42" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>135817457</v>
       </c>
       <c r="B43" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135825727</v>
       </c>
       <c r="B44" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>135825937</v>
       </c>
       <c r="B45" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>135825994</v>
       </c>
       <c r="B46" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>135810638</v>
       </c>
       <c r="B47" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>135810678</v>
       </c>
       <c r="B48" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>135810752</v>
       </c>
       <c r="B49" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>135811260</v>
       </c>
       <c r="B50" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>135811380</v>
       </c>
       <c r="B51" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>135811775</v>
       </c>
       <c r="B52" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>135811889</v>
       </c>
       <c r="B53" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>135812149</v>
       </c>
       <c r="B54" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>135812282</v>
       </c>
       <c r="B55" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>135812304</v>
       </c>
       <c r="B56" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>135812678</v>
       </c>
       <c r="B57" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>135813207</v>
       </c>
       <c r="B58" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>135813220</v>
       </c>
       <c r="B59" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>135813260</v>
       </c>
       <c r="B60" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>135813643</v>
       </c>
       <c r="B61" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>135813806</v>
       </c>
       <c r="B62" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>135815937</v>
       </c>
       <c r="B63" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>135816847</v>
       </c>
       <c r="B64" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>135817411</v>
       </c>
       <c r="B65" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>135817908</v>
       </c>
       <c r="B66" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>135818950</v>
       </c>
       <c r="B67" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>135820000</v>
       </c>
       <c r="B68" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>135820108</v>
       </c>
       <c r="B69" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135820167</v>
       </c>
       <c r="B70" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>135820223</v>
       </c>
       <c r="B71" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>135824350</v>
       </c>
       <c r="B72" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>135824747</v>
       </c>
       <c r="B73" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>135824805</v>
       </c>
       <c r="B74" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>135825271</v>
       </c>
       <c r="B75" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>135825839</v>
       </c>
       <c r="B76" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>135826009</v>
       </c>
       <c r="B77" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>135817961</v>
       </c>
       <c r="B78" t="n">
-        <v>57171</v>
+        <v>57184</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>135810576</v>
       </c>
       <c r="B79" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>135825534</v>
       </c>
       <c r="B80" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>135825749</v>
       </c>
       <c r="B81" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>135825755</v>
       </c>
       <c r="B82" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>135824162</v>
       </c>
       <c r="B83" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>135824255</v>
       </c>
       <c r="B84" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>135825266</v>
       </c>
       <c r="B85" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
